--- a/output/pdf_financials_xlsx/MSM.xlsx
+++ b/output/pdf_financials_xlsx/MSM.xlsx
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
     </row>
     <row r="92">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.057178</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.057178</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.028418</v>
       </c>
     </row>
     <row r="93">
@@ -2951,7 +2951,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2980,7 +2984,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3172,7 +3180,11 @@
           <t>Reserves (note 5)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>0.057178</v>
       </c>

--- a/output/pdf_financials_xlsx/MSM.xlsx
+++ b/output/pdf_financials_xlsx/MSM.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000683</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
     </row>
     <row r="13">
@@ -864,10 +864,10 @@
         <v>-0.638025</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.7637350000000001</v>
+        <v>-0.764418</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.702491</v>
+        <v>-0.702496</v>
       </c>
     </row>
     <row r="28">
@@ -896,10 +896,10 @@
         <v>-0.638025</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.7637350000000001</v>
+        <v>-0.764418</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.702491</v>
+        <v>-0.702496</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.138484</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.017688</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.064842</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.138484</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.017688</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.064842</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.159175</v>
+        <v>0.020691</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.014287</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.069842</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="49">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">

--- a/output/pdf_financials_xlsx/MSM.xlsx
+++ b/output/pdf_financials_xlsx/MSM.xlsx
@@ -2069,7 +2069,7 @@
         <v>0.043265</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000321</v>
       </c>
     </row>
     <row r="102">
@@ -2149,7 +2149,7 @@
         <v>0.252188</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.12344</v>
+        <v>-0.123761</v>
       </c>
     </row>
     <row r="107">
@@ -3393,7 +3393,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
